--- a/wünsche.xlsx
+++ b/wünsche.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Dateien\Programmieren\w0fl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEBD275B-1D78-4BA9-A8E1-BA0392694272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD5EF809-2B81-4846-9405-6597B7731528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{9F29547C-95CE-47C1-A685-E4A01FDA0794}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2" xr2:uid="{9F29547C-95CE-47C1-A685-E4A01FDA0794}"/>
   </bookViews>
   <sheets>
     <sheet name="Wishlist" sheetId="1" r:id="rId1"/>
     <sheet name="Magic" sheetId="3" r:id="rId2"/>
     <sheet name="Carrera" sheetId="4" r:id="rId3"/>
+    <sheet name="PC" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="121">
   <si>
     <t>Name</t>
   </si>
@@ -61,45 +62,6 @@
     <t>https://www.mediamarkt.de/de/product/_usb-germany--metall-kreditkarte-usb-stick-schw-89446557.html</t>
   </si>
   <si>
-    <t>Märklin 29000 Digital-Startset Mobile Station 2</t>
-  </si>
-  <si>
-    <t>https://www.modellbahnunion.com/Spur-H0/Digital-Startset-Mobile-Station-2-Schienen.htm?a=article&amp;ProdNr=Marklin-29000&amp;p=802</t>
-  </si>
-  <si>
-    <t>Digital-Startset Mobile Station 2 (aus Kempten)</t>
-  </si>
-  <si>
-    <t>https://www.slotblog.de/produkt/carrera-randstreifenpaket-fuer-die-grundpackung-300015-dtm-speed-memories/</t>
-  </si>
-  <si>
-    <t>Carrera Randstreifenpaket für die Grundpackung 30015 DTM Speed Memories</t>
-  </si>
-  <si>
-    <t>https://www.slotblog.de/produkt/randstreifenpaket-fuer-die-carrera-digital-132-retro-grand-prix/</t>
-  </si>
-  <si>
-    <t>Randstreifenpaket für die Carrera Digital 132 Retro Grand Prix</t>
-  </si>
-  <si>
-    <t>Acura ARX-5 Daytona 2022 #60 Analog / Carrera Digital 132</t>
-  </si>
-  <si>
-    <t>https://www.overdrive-shop.com/Acura-ARX-5-Daytona-2022-60-Analog-Carrera-Digital-132#cfg-container</t>
-  </si>
-  <si>
-    <t>https://www.overdrive-shop.com/Porsche-963-LM-H-LeMans-2023-75-Analog-Carrera-Digital-132</t>
-  </si>
-  <si>
-    <t>Porsche 963 LM-H LeMans 2023 #75 Analog / Carrera Digital 132</t>
-  </si>
-  <si>
-    <t>HyperX Wrist Rest – Tastatur – ohne Ziffernblock</t>
-  </si>
-  <si>
-    <t>https://de.hyperx.com/products/hyperx-wrist-rest-tenkeyless?variant=40706501214344</t>
-  </si>
-  <si>
     <t>Longboardteile</t>
   </si>
   <si>
@@ -145,57 +107,9 @@
     <t>The Eternity Elevator</t>
   </si>
   <si>
-    <t>https://www.caseking.de/asrock-radeon-rx-9070-xt-taichi-oc-graphics-card-16384-mb-gddr6/GCAR-029.html</t>
-  </si>
-  <si>
-    <t>ASrock Radeon RX 9070 XT Taichi 16GB</t>
-  </si>
-  <si>
-    <t>1000 Watt be quiet! Straight Power 12 Modular 80+ Platinum</t>
-  </si>
-  <si>
-    <t>https://www.mindfactory.de/product_info.php/1000-Watt-be-quiet--Straight-Power-12-Modular-80--Platinum_1496098.html</t>
-  </si>
-  <si>
-    <t>32GB G.Skill Trident Z RGB DDR4-3600 DIMM CL18</t>
-  </si>
-  <si>
-    <t>https://www.mindfactory.de/product_info.php/32GB-G-Skill-Trident-Z-RGB-DDR4-3600-DIMM-CL18-Dual-Kit_1334014.html</t>
-  </si>
-  <si>
-    <t>https://www.caseking.de/be-quiet-mc1-m.2-ssd-cooler-black/ZUWE-441.html</t>
-  </si>
-  <si>
-    <t>be quiet! MC1 M.2 SSD Kühler - schwarz</t>
-  </si>
-  <si>
-    <t>Alpenföhn 120mm Wing Boost 3 ARGB High Speed</t>
-  </si>
-  <si>
-    <t>https://www.caseking.de/alpenfoehn-120mm-wing-boost-3-argb-high-speed-pwm-fans-triple-black/LUAL-040.html</t>
-  </si>
-  <si>
-    <t>be quiet! CP-6610 PCIe Single-Kabel</t>
-  </si>
-  <si>
-    <t>https://www.caseking.de/be-quiet-cp-6610-pcie-single-cable-for-modular-power-supplies-black/NEDE-043.html</t>
-  </si>
-  <si>
-    <t>https://www.caseking.de/inline-spiral-binding-cable-sleeve-black-10mm-x-10m/ZUSP-009.html</t>
-  </si>
-  <si>
-    <t>InLine Spiralband Kabelschlauch, schwarz - 10mm x 10m</t>
-  </si>
-  <si>
     <t>Zusammen:</t>
   </si>
   <si>
-    <t>CableMod Universal Pro ModMesh 16-Pin zu 16-Pin-Kabel, 90° Anschluss, Sleeved, StealthSense - schwarz, 60 cm, Var. B</t>
-  </si>
-  <si>
-    <t>https://www.caseking.de/cablemod-universal-pro-modmesh-16-pin-to-16-pin-cable-90-connector-sleeved-stealthsense-black-60-cm-var.-b/ZUAD-1726.html</t>
-  </si>
-  <si>
     <t>Bruna, the Fading Light</t>
   </si>
   <si>
@@ -232,9 +146,6 @@
     <t>Partner</t>
   </si>
   <si>
-    <t>https://www.slotcarscheune.de/Bahn-Zubehoer/Carrera/Carrera-233/kurven-und-randstreifen/Carrera-Innenrandstreifen-Komplett-fuer-Kurve-1-60-20020551-4281.html</t>
-  </si>
-  <si>
     <t>Autos</t>
   </si>
   <si>
@@ -304,9 +215,6 @@
     <t>49d, 33bv</t>
   </si>
   <si>
-    <t>33b</t>
-  </si>
-  <si>
     <t>33bv</t>
   </si>
   <si>
@@ -343,39 +251,9 @@
     <t>33p</t>
   </si>
   <si>
-    <t>https://www.gokarli.de/Carrera-Digital-132-Evolution-Reifen-Porsche-GT3-RSR-89552</t>
-  </si>
-  <si>
     <t>At.nr,</t>
   </si>
   <si>
-    <t>https://www.gokarli.de/Ortmann-Reifen-33P</t>
-  </si>
-  <si>
-    <t>https://www.gokarli.de/Carrera-Digital-132-Evolution-Reifen-89800-fuer-DTM-ab-2012-Corvette-Aston-Martin-BMWZ4-und-mehr</t>
-  </si>
-  <si>
-    <t>https://www.gokarli.de/Carrera-Digital-132-Evolution-Reifen-Tomaso-Pantera-27263-27264-27671-27672-27720-27721-30990-30991-31044-31045</t>
-  </si>
-  <si>
-    <t>https://www.gokarli.de/Ortmann-Reifen-33J</t>
-  </si>
-  <si>
-    <t>https://www.gokarli.de/Carrera-Digital-132-Evolution-Reifen-Lamborghini-Huracan-GT3-KTM-X-BOW-GT2-GTX-89919</t>
-  </si>
-  <si>
-    <t>https://www.gokarli.de/Ortmann-Reifen-49D, https://www.gokarli.de/Ortmann-Reifen-33L</t>
-  </si>
-  <si>
-    <t>https://www.gokarli.de/Carrera-Digital-132-Evolution-Reifen-89705-27403-27381-27382-27403-27427-30551-30552-30611-30612-30640-31034</t>
-  </si>
-  <si>
-    <t>https://www.gokarli.de/Carrera-Digital-132-Evolution-Reifen-Mercedes-SLS-AMG-89715</t>
-  </si>
-  <si>
-    <t>https://www.gokarli.de/DSM-RC-Flexibler-Slotcar-Spoiler-kompatibel-zu-Carrera-Evolution-Digital-132-Porsche-911-RSR</t>
-  </si>
-  <si>
     <t>https://www.gokarli.de/DSM-RC-Flexibler-Slotcar-Spoiler-kompatibel-zu-Carrera-Evolution-Digital-132-BMW-M4-DTM</t>
   </si>
   <si>
@@ -383,16 +261,170 @@
   </si>
   <si>
     <t>https://www.gokarli.de/DSM-RC-Flexibler-Slotcar-Spoiler-kompatibel-zu-Carrera-Evolution-Digital-132-Corvette-C8R</t>
+  </si>
+  <si>
+    <t>49aog</t>
+  </si>
+  <si>
+    <t>33z</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 33b</t>
+  </si>
+  <si>
+    <t>Porsche 911 RSR "Pink Pig Design"</t>
+  </si>
+  <si>
+    <t>Aston Martin Vantage AMR GT3 EVO "Walkenhorst Motorsport"</t>
+  </si>
+  <si>
+    <t>PC - Ifself</t>
+  </si>
+  <si>
+    <t>Peripherie</t>
+  </si>
+  <si>
+    <t>Setup</t>
+  </si>
+  <si>
+    <t>Microsoft LifeCam Studio</t>
+  </si>
+  <si>
+    <t>SSD 2TB Kingston NV1 M.2 PCIe 3.0 x4</t>
+  </si>
+  <si>
+    <t>MB ASRock Pro RS Intel Z690 So. 1700</t>
+  </si>
+  <si>
+    <t>Alt - Teile</t>
+  </si>
+  <si>
+    <t>LC-Power Gaming 993B Midi Tower</t>
+  </si>
+  <si>
+    <t>SSD 500GB Crucial MX500 2.5"</t>
+  </si>
+  <si>
+    <t>12GB MSI GeForce RTX 3060 Ventus 2X OC</t>
+  </si>
+  <si>
+    <t>4TB Seagate IronWolf Pro NAS</t>
+  </si>
+  <si>
+    <t>be quiet! MB Sleeved Power Cable CB-6620</t>
+  </si>
+  <si>
+    <t>Corsair Lighting Node Pro Set</t>
+  </si>
+  <si>
+    <t>1000 Watt be quiet! Pure Power 13</t>
+  </si>
+  <si>
+    <t>PSU 750 Watt be quiet! Straight Power 11</t>
+  </si>
+  <si>
+    <t>CPU Intel Core i7 13700K 16 (8+8)</t>
+  </si>
+  <si>
+    <t>LG Monitor Kleinanzeigen IPS Damaged</t>
+  </si>
+  <si>
+    <t>Philips 24" V Line LCD (Euronics)</t>
+  </si>
+  <si>
+    <t>27" 200Hz iiyama G-MASTER G2771QS-B1 Red Eagle</t>
+  </si>
+  <si>
+    <t>24,5" (62,23cm) MSI Optix G251PF 165Hz</t>
+  </si>
+  <si>
+    <t>Alpenföhn Gletscherwasser 360 High Speed</t>
+  </si>
+  <si>
+    <t>Alpenföhn 120mm Wing Boost 3 ARGB High Speed 3x</t>
+  </si>
+  <si>
+    <t>Thermal Grizzly CPU Contact Frame</t>
+  </si>
+  <si>
+    <r>
+      <t>MSI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> GeForce RTX 5080 GAMING TRIO OC</t>
+    </r>
+  </si>
+  <si>
+    <t>Everest Max - German ISO / MX Brown / Midnight Black</t>
+  </si>
+  <si>
+    <t>Glaze GPL205G0 Lube</t>
+  </si>
+  <si>
+    <t>Höhenverstellbarer Schreibtisch E7 2026</t>
+  </si>
+  <si>
+    <t>Titanwolf Gaming Mauspad, XXL</t>
+  </si>
+  <si>
+    <t>G801 Logitech Tastatur</t>
+  </si>
+  <si>
+    <t>G502 Logitech Maus</t>
+  </si>
+  <si>
+    <t>6GB Asus GTX 1060</t>
+  </si>
+  <si>
+    <t>Nyfpad XXL Koi Premium Gaming Mousepad</t>
+  </si>
+  <si>
+    <t>Maus Logitech G502 X Lightspeed</t>
+  </si>
+  <si>
+    <t>Auna Mikrophone</t>
+  </si>
+  <si>
+    <t>HyperX Wristrest</t>
+  </si>
+  <si>
+    <t>Managed Switch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holz im Pc </t>
+  </si>
+  <si>
+    <t>Plastik im Pc</t>
+  </si>
+  <si>
+    <t>USB Hub</t>
+  </si>
+  <si>
+    <t>Controller PowerA</t>
+  </si>
+  <si>
+    <t>16GB Corsair Vengeance LPX schwarz DDR4-3200 4x</t>
+  </si>
+  <si>
+    <t>G.Skill TridentZ DDR4 32 GB 2 x 16 GB 3200 MHz 2x</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-407]_-;\-* #,##0.00\ [$€-407]_-;_-* &quot;-&quot;??\ [$€-407]_-;_-@_-"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -413,6 +445,19 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -687,11 +732,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -723,17 +769,15 @@
       </extLst>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
-      </extLst>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Währung" xfId="2" builtinId="4"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1091,7 +1135,7 @@
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
   <dimension ref="B3:F36"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="0" hidden="1" customWidth="1"/>
     <col min="2" max="3" width="11.42578125" hidden="1" customWidth="1"/>
@@ -1135,23 +1179,13 @@
       </c>
     </row>
     <row r="7" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="8">
-        <v>180</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>8</v>
-      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="10"/>
     </row>
     <row r="8" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="8">
-        <v>140</v>
-      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="8"/>
       <c r="F8" s="5"/>
     </row>
     <row r="9" spans="4:6" x14ac:dyDescent="0.25">
@@ -1160,55 +1194,29 @@
       <c r="F9" s="10"/>
     </row>
     <row r="10" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="8">
-        <v>120</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>10</v>
-      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="10"/>
     </row>
     <row r="11" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="8">
-        <v>125</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>12</v>
-      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="10"/>
     </row>
     <row r="12" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="8">
-        <v>150</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>15</v>
-      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="10"/>
     </row>
     <row r="13" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D13" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="8">
-        <v>168</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>16</v>
-      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="10"/>
     </row>
     <row r="14" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D14" s="19"/>
       <c r="E14" s="20"/>
-      <c r="F14" s="22" t="s">
-        <v>64</v>
-      </c>
+      <c r="F14" s="22"/>
     </row>
     <row r="15" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D15" s="19"/>
@@ -1221,101 +1229,49 @@
       <c r="F16" s="5"/>
     </row>
     <row r="17" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D17" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E17" s="8">
-        <v>820</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>35</v>
-      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="10"/>
     </row>
     <row r="18" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D18" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E18" s="8">
-        <v>180</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>38</v>
-      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="10"/>
     </row>
     <row r="19" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D19" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E19" s="8">
-        <v>100</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>40</v>
-      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="10"/>
     </row>
     <row r="20" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D20" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E20" s="8">
-        <v>100</v>
-      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="8"/>
       <c r="F20" s="5"/>
     </row>
     <row r="21" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D21" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E21" s="8">
-        <v>10</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>41</v>
-      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="10"/>
     </row>
     <row r="22" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D22" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E22" s="8">
-        <v>50</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>44</v>
-      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="10"/>
     </row>
     <row r="23" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D23" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E23" s="8">
-        <v>30</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>51</v>
-      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="10"/>
     </row>
     <row r="24" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D24" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E24" s="8">
-        <v>10</v>
-      </c>
-      <c r="F24" s="10" t="s">
-        <v>46</v>
-      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="10"/>
     </row>
     <row r="25" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D25" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E25" s="8">
-        <v>5</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>47</v>
-      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="10"/>
     </row>
     <row r="26" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D26" s="4"/>
@@ -1344,11 +1300,11 @@
     </row>
     <row r="31" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D31" s="4" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="E31" s="8">
         <f>SUM(E17:E29)</f>
-        <v>1305</v>
+        <v>0</v>
       </c>
       <c r="F31" s="5"/>
     </row>
@@ -1358,15 +1314,9 @@
       <c r="F32" s="5"/>
     </row>
     <row r="33" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D33" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E33" s="12">
-        <v>20</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>19</v>
-      </c>
+      <c r="D33" s="11"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="13"/>
     </row>
     <row r="34" spans="4:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D34" s="6"/>
@@ -1375,28 +1325,16 @@
     </row>
     <row r="36" spans="4:6" x14ac:dyDescent="0.25">
       <c r="E36" s="18" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="F36" s="17" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F7" r:id="rId1" xr:uid="{B3C301B0-0643-4919-B0E6-822E79ACEAD8}"/>
-    <hyperlink ref="F6" r:id="rId2" xr:uid="{90C88114-7627-4494-8C30-DA96E3807496}"/>
-    <hyperlink ref="F5" r:id="rId3" xr:uid="{0A379125-3A72-4E57-9F78-717BE7E120E3}"/>
-    <hyperlink ref="F24" r:id="rId4" xr:uid="{61A2E3D5-953A-49EA-9439-A2FCF9F5B288}"/>
-    <hyperlink ref="F25" r:id="rId5" xr:uid="{2720F716-1C44-44C4-9D74-BE38E3ED9A13}"/>
-    <hyperlink ref="F23" r:id="rId6" xr:uid="{5B1ABBA9-954D-454E-87DA-26B85ACBEAC7}"/>
-    <hyperlink ref="F22" r:id="rId7" xr:uid="{4F08F0CC-03BA-459C-9957-F4016A6C6052}"/>
-    <hyperlink ref="F21" r:id="rId8" xr:uid="{4C97DBE6-3868-4F94-8198-64989AE32EFA}"/>
-    <hyperlink ref="F19" r:id="rId9" xr:uid="{AC12DB56-ABE6-43CA-AFFA-DF1FC98AF69D}"/>
-    <hyperlink ref="F18" r:id="rId10" xr:uid="{C853E9D4-3631-42F0-9502-9F2A07DA1178}"/>
-    <hyperlink ref="F17" r:id="rId11" xr:uid="{1CB4B0AF-E0ED-4302-9A0C-D3ECF97A73B0}"/>
-    <hyperlink ref="F10" r:id="rId12" xr:uid="{1966C120-2C3C-4C14-AD10-51403DFA2ECF}"/>
-    <hyperlink ref="F11" r:id="rId13" xr:uid="{7182295F-DA77-4E5A-9F38-5B191200B45C}"/>
-    <hyperlink ref="F14" r:id="rId14" xr:uid="{8F3D2448-CEC0-4778-B2E5-519E73BE2066}"/>
+    <hyperlink ref="F6" r:id="rId1" xr:uid="{90C88114-7627-4494-8C30-DA96E3807496}"/>
+    <hyperlink ref="F5" r:id="rId2" xr:uid="{0A379125-3A72-4E57-9F78-717BE7E120E3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1408,7 +1346,7 @@
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
   <dimension ref="B3:F34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="0" hidden="1" customWidth="1"/>
     <col min="2" max="3" width="11.42578125" hidden="1" customWidth="1"/>
@@ -1431,51 +1369,51 @@
     </row>
     <row r="5" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D5" s="4" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E5" s="8">
         <v>22</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D6" s="4" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E6" s="8">
         <v>5</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D7" s="4" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E7" s="8">
         <v>25</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D8" s="4" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="E8" s="8">
         <v>10</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D9" s="4" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="E9" s="8">
         <v>30</v>
@@ -1484,7 +1422,7 @@
     </row>
     <row r="10" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D10" s="4" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E10" s="8"/>
       <c r="F10" s="10"/>
@@ -1501,7 +1439,7 @@
     </row>
     <row r="13" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D13" s="4" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="E13" s="8">
         <v>2</v>
@@ -1510,7 +1448,7 @@
     </row>
     <row r="14" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D14" s="4" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E14" s="8">
         <v>1</v>
@@ -1534,7 +1472,7 @@
     </row>
     <row r="18" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D18" s="4" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="E18" s="8">
         <v>2.5</v>
@@ -1543,7 +1481,7 @@
     </row>
     <row r="19" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D19" s="4" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="E19" s="8">
         <v>10</v>
@@ -1552,14 +1490,14 @@
     </row>
     <row r="20" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D20" s="4" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="E20" s="8"/>
       <c r="F20" s="5"/>
     </row>
     <row r="21" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D21" s="4" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="E21" s="8">
         <v>20</v>
@@ -1568,7 +1506,7 @@
     </row>
     <row r="22" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D22" s="4" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="E22" s="8">
         <v>0.3</v>
@@ -1577,7 +1515,7 @@
     </row>
     <row r="23" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D23" s="4" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="E23" s="8">
         <v>4</v>
@@ -1586,7 +1524,7 @@
     </row>
     <row r="24" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D24" s="4" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="E24" s="8">
         <v>5</v>
@@ -1595,7 +1533,7 @@
     </row>
     <row r="25" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D25" s="4" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="E25" s="8">
         <v>3</v>
@@ -1604,7 +1542,7 @@
     </row>
     <row r="26" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D26" s="4" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="E26" s="8">
         <v>3</v>
@@ -1613,7 +1551,7 @@
     </row>
     <row r="27" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D27" s="4" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="E27" s="8">
         <v>25</v>
@@ -1622,13 +1560,13 @@
     </row>
     <row r="28" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D28" s="14" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E28" s="15">
         <v>7</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="4:6" x14ac:dyDescent="0.25">
@@ -1658,7 +1596,7 @@
     </row>
     <row r="34" spans="4:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D34" s="6" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E34" s="9">
         <v>0.4</v>
@@ -1678,7 +1616,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73A0406A-C75F-4329-8AFF-555E9659B696}">
   <dimension ref="A1:G29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="74.28515625" customWidth="1"/>
     <col min="2" max="2" width="6.140625" customWidth="1"/>
@@ -1690,36 +1628,36 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="B1" s="21" t="s">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="D1" s="21" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="F1" s="21" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B2">
         <v>30570</v>
       </c>
-      <c r="C2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D2" t="s">
-        <v>84</v>
+      <c r="C2" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>54</v>
       </c>
       <c r="E2" s="23" t="b">
         <v>1</v>
@@ -1727,265 +1665,268 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="B3">
         <v>30986</v>
       </c>
-      <c r="C3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D3" t="s">
-        <v>86</v>
+      <c r="C3" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>56</v>
       </c>
       <c r="E3" s="23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="G3" s="24" t="s">
-        <v>112</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="B4">
         <v>31015</v>
       </c>
-      <c r="C4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D4" t="s">
-        <v>88</v>
+      <c r="C4" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>76</v>
       </c>
       <c r="E4" s="23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="G4" s="24" t="s">
-        <v>114</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="B5">
         <v>31044</v>
       </c>
-      <c r="C5" t="s">
-        <v>91</v>
-      </c>
-      <c r="D5" t="s">
-        <v>90</v>
+      <c r="C5" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>59</v>
       </c>
       <c r="E5" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" s="24" t="s">
-        <v>105</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="B6">
         <v>30971</v>
       </c>
-      <c r="D6" t="s">
-        <v>92</v>
+      <c r="D6" s="26" t="s">
+        <v>61</v>
       </c>
       <c r="E6" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="F6" s="24" t="s">
-        <v>106</v>
-      </c>
+      <c r="F6" s="24"/>
       <c r="G6" s="24"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="B7">
         <v>31012</v>
       </c>
-      <c r="C7" t="s">
-        <v>95</v>
-      </c>
-      <c r="D7" t="s">
-        <v>94</v>
+      <c r="C7" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>63</v>
       </c>
       <c r="E7" s="23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="24" t="s">
-        <v>107</v>
-      </c>
-      <c r="G7" s="24" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="B8">
         <v>30523</v>
       </c>
-      <c r="C8" t="s">
-        <v>97</v>
-      </c>
-      <c r="D8" t="s">
-        <v>96</v>
+      <c r="C8" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>65</v>
       </c>
       <c r="E8" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" t="s">
-        <v>108</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="B9">
         <v>30846</v>
       </c>
-      <c r="C9" t="s">
-        <v>89</v>
-      </c>
-      <c r="D9" t="s">
-        <v>98</v>
+      <c r="C9" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>67</v>
       </c>
       <c r="E9" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="F9" s="25" t="s">
-        <v>104</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F9" s="24"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="B10">
         <v>31034</v>
       </c>
-      <c r="C10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D10" t="s">
-        <v>98</v>
+      <c r="C10" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>67</v>
       </c>
       <c r="E10" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" s="24" t="s">
-        <v>109</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F10" s="24"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="B11">
         <v>30793</v>
       </c>
-      <c r="C11" t="s">
-        <v>99</v>
-      </c>
-      <c r="D11" t="s">
-        <v>99</v>
+      <c r="C11" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>68</v>
       </c>
       <c r="E11" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" s="24" t="s">
-        <v>110</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F11" s="24"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="B12">
         <v>27566</v>
       </c>
+      <c r="C12" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>74</v>
+      </c>
       <c r="E12" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="F12" s="24" t="s">
-        <v>101</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F12" s="24"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="B13">
         <v>30915</v>
       </c>
-      <c r="C13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D13" t="s">
-        <v>98</v>
+      <c r="C13" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" s="26" t="s">
+        <v>67</v>
       </c>
       <c r="E13" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" s="24" t="s">
-        <v>104</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F13" s="24"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="B14">
         <v>32019</v>
       </c>
-      <c r="C14" t="s">
-        <v>89</v>
-      </c>
-      <c r="D14" t="s">
-        <v>98</v>
+      <c r="C14" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="26" t="s">
+        <v>67</v>
       </c>
       <c r="E14" s="23" t="b">
         <v>1</v>
       </c>
-      <c r="F14" s="24" t="s">
-        <v>111</v>
-      </c>
+      <c r="F14" s="24"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="B15">
         <v>30521</v>
       </c>
-      <c r="D15" t="s">
-        <v>100</v>
+      <c r="D15" s="26" t="s">
+        <v>69</v>
       </c>
       <c r="E15" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="F15" s="24" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F15" s="24"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16" s="23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17" s="23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1993,22 +1934,323 @@
     <sortCondition ref="A2:A15"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="F9" r:id="rId1" xr:uid="{70ACCCA8-3700-4E55-B763-3D48B275DC2C}"/>
-    <hyperlink ref="G7" r:id="rId2" xr:uid="{854160ED-0DB9-4A04-9DBE-594274A311FC}"/>
-    <hyperlink ref="G4" r:id="rId3" xr:uid="{88E82DFC-EB42-4529-B950-47CB73D83A3E}"/>
-    <hyperlink ref="G3" r:id="rId4" xr:uid="{389A271B-8030-4471-B0B2-427E7173FFA1}"/>
-    <hyperlink ref="F3" r:id="rId5" xr:uid="{1B4DD302-ABA1-43BF-981D-A256E03FFC52}"/>
-    <hyperlink ref="F4" r:id="rId6" xr:uid="{5A428356-D46B-4D7A-A0D1-7F9000C5998E}"/>
-    <hyperlink ref="F5" r:id="rId7" xr:uid="{25DE3FDD-8651-4DDD-AEEF-180CF4F1EF12}"/>
-    <hyperlink ref="F7" r:id="rId8" xr:uid="{13CEDDC9-B7E1-4948-B995-893AA14CF8EC}"/>
-    <hyperlink ref="F10" r:id="rId9" xr:uid="{A26D0F1E-582F-4448-8BE8-6000AFDD3FC6}"/>
-    <hyperlink ref="F11" r:id="rId10" xr:uid="{83B3CE6A-A54E-43D0-BD73-9EAAF568E4D1}"/>
-    <hyperlink ref="F12" r:id="rId11" xr:uid="{CAC590DE-116D-484D-B41D-C66972DB687E}"/>
-    <hyperlink ref="F13" r:id="rId12" xr:uid="{1BE380A2-D35B-491A-BE54-512827568A37}"/>
-    <hyperlink ref="F14" r:id="rId13" xr:uid="{B2F5C803-3AA3-408D-A331-92B1245798FB}"/>
-    <hyperlink ref="F15" r:id="rId14" xr:uid="{717F05A8-370E-4C7B-8BFF-6CF1D27FA654}"/>
-    <hyperlink ref="F6" r:id="rId15" xr:uid="{D076C418-E852-4D95-950B-90BB92D4134D}"/>
+    <hyperlink ref="F7" r:id="rId1" xr:uid="{854160ED-0DB9-4A04-9DBE-594274A311FC}"/>
+    <hyperlink ref="F4" r:id="rId2" xr:uid="{88E82DFC-EB42-4529-B950-47CB73D83A3E}"/>
+    <hyperlink ref="F3" r:id="rId3" xr:uid="{389A271B-8030-4471-B0B2-427E7173FFA1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEA1F57F-BFF6-4B16-8AC7-25E1199E4A61}">
+  <dimension ref="A1:K21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="47.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" style="27"/>
+    <col min="3" max="3" width="4.28515625" style="27" customWidth="1"/>
+    <col min="4" max="4" width="50.140625" customWidth="1"/>
+    <col min="5" max="5" width="12" style="27" customWidth="1"/>
+    <col min="6" max="6" width="3.85546875" style="27" customWidth="1"/>
+    <col min="7" max="7" width="45.42578125" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" style="27" customWidth="1"/>
+    <col min="9" max="9" width="3.5703125" style="27" customWidth="1"/>
+    <col min="10" max="10" width="51" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" style="27"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" s="27">
+        <v>144.88999999999999</v>
+      </c>
+      <c r="D3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E3" s="27">
+        <v>64.709999999999994</v>
+      </c>
+      <c r="G3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H3" s="27">
+        <v>299.99</v>
+      </c>
+      <c r="J3" t="s">
+        <v>86</v>
+      </c>
+      <c r="K3" s="27">
+        <v>54.73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="27">
+        <v>209.09</v>
+      </c>
+      <c r="D4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E4" s="27">
+        <v>229</v>
+      </c>
+      <c r="G4" t="s">
+        <v>110</v>
+      </c>
+      <c r="H4" s="27">
+        <v>30</v>
+      </c>
+      <c r="J4" t="s">
+        <v>119</v>
+      </c>
+      <c r="K4" s="27">
+        <v>115.04</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="27">
+        <v>34.75</v>
+      </c>
+      <c r="D5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E5" s="27">
+        <v>164.61</v>
+      </c>
+      <c r="G5" t="s">
+        <v>113</v>
+      </c>
+      <c r="H5" s="27">
+        <v>20</v>
+      </c>
+      <c r="J5" t="s">
+        <v>88</v>
+      </c>
+      <c r="K5" s="27">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B6" s="27">
+        <v>111.99</v>
+      </c>
+      <c r="D6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E6" s="27">
+        <v>110</v>
+      </c>
+      <c r="G6" t="s">
+        <v>115</v>
+      </c>
+      <c r="H6" s="27">
+        <v>20</v>
+      </c>
+      <c r="J6" t="s">
+        <v>93</v>
+      </c>
+      <c r="K6" s="27">
+        <v>121.88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" s="27">
+        <v>14.05</v>
+      </c>
+      <c r="D7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" s="27">
+        <v>99.99</v>
+      </c>
+      <c r="G7" t="s">
+        <v>116</v>
+      </c>
+      <c r="H7" s="27">
+        <v>10</v>
+      </c>
+      <c r="J7" t="s">
+        <v>95</v>
+      </c>
+      <c r="K7" s="27">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" s="27">
+        <v>47.56</v>
+      </c>
+      <c r="D8" t="s">
+        <v>104</v>
+      </c>
+      <c r="E8" s="27">
+        <v>19.989999999999998</v>
+      </c>
+      <c r="J8" t="s">
+        <v>106</v>
+      </c>
+      <c r="K8" s="27">
+        <v>19.95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" s="27">
+        <v>149.93</v>
+      </c>
+      <c r="D9" t="s">
+        <v>111</v>
+      </c>
+      <c r="E9" s="27">
+        <v>79.75</v>
+      </c>
+      <c r="J9" t="s">
+        <v>107</v>
+      </c>
+      <c r="K9" s="27">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" s="27">
+        <v>508</v>
+      </c>
+      <c r="D10" t="s">
+        <v>112</v>
+      </c>
+      <c r="E10" s="27">
+        <v>80</v>
+      </c>
+      <c r="J10" t="s">
+        <v>108</v>
+      </c>
+      <c r="K10" s="27">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B11" s="27">
+        <v>180</v>
+      </c>
+      <c r="D11" t="s">
+        <v>114</v>
+      </c>
+      <c r="E11" s="27">
+        <v>25</v>
+      </c>
+      <c r="J11" t="s">
+        <v>109</v>
+      </c>
+      <c r="K11" s="27">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B12" s="27">
+        <v>49.9</v>
+      </c>
+      <c r="D12" t="s">
+        <v>117</v>
+      </c>
+      <c r="E12" s="27">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>101</v>
+      </c>
+      <c r="B13" s="27">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="D13" t="s">
+        <v>118</v>
+      </c>
+      <c r="E13" s="27">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="B14" s="27">
+        <v>1163.0899999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>120</v>
+      </c>
+      <c r="B15">
+        <v>234.98</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B21" s="27">
+        <f>SUM(B3:B17)</f>
+        <v>2868.13</v>
+      </c>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27">
+        <f t="shared" ref="E21:K21" si="0">SUM(E3:E17)</f>
+        <v>933.05</v>
+      </c>
+      <c r="G21" s="27"/>
+      <c r="H21" s="27">
+        <f t="shared" si="0"/>
+        <v>379.99</v>
+      </c>
+      <c r="J21" s="27"/>
+      <c r="K21" s="27">
+        <f t="shared" si="0"/>
+        <v>995.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>